--- a/review-results/河北实时运行及市场出清数据-20260801.xlsx
+++ b/review-results/河北实时运行及市场出清数据-20260801.xlsx
@@ -1386,8 +1386,12 @@
       <s:c r="C2" s="11" t="n">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="D2" s="12"/>
-      <s:c r="E2" s="13"/>
+      <s:c r="D2" s="12" t="n">
+        <s:v>35191.2</s:v>
+      </s:c>
+      <s:c r="E2" s="13" t="n">
+        <s:v>9955.77</s:v>
+      </s:c>
       <s:c r="F2" s="14" t="n">
         <s:v>2999.2</s:v>
       </s:c>
@@ -1410,8 +1414,12 @@
       <s:c r="C3" s="11" t="n">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="D3" s="12"/>
-      <s:c r="E3" s="13"/>
+      <s:c r="D3" s="12" t="n">
+        <s:v>34898.3</s:v>
+      </s:c>
+      <s:c r="E3" s="13" t="n">
+        <s:v>9774.19</s:v>
+      </s:c>
       <s:c r="F3" s="14" t="n">
         <s:v>3135.3</s:v>
       </s:c>
@@ -1434,8 +1442,12 @@
       <s:c r="C4" s="11" t="n">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="D4" s="12"/>
-      <s:c r="E4" s="13"/>
+      <s:c r="D4" s="12" t="n">
+        <s:v>34623</s:v>
+      </s:c>
+      <s:c r="E4" s="13" t="n">
+        <s:v>9292.71</s:v>
+      </s:c>
       <s:c r="F4" s="14" t="n">
         <s:v>3139.2</s:v>
       </s:c>
@@ -1458,8 +1470,12 @@
       <s:c r="C5" s="11" t="n">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="D5" s="12"/>
-      <s:c r="E5" s="13"/>
+      <s:c r="D5" s="12" t="n">
+        <s:v>34576.9</s:v>
+      </s:c>
+      <s:c r="E5" s="13" t="n">
+        <s:v>8940.46</s:v>
+      </s:c>
       <s:c r="F5" s="14" t="n">
         <s:v>3052.3</s:v>
       </s:c>
@@ -1482,8 +1498,12 @@
       <s:c r="C6" s="11" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="D6" s="12"/>
-      <s:c r="E6" s="13"/>
+      <s:c r="D6" s="12" t="n">
+        <s:v>36679.3</s:v>
+      </s:c>
+      <s:c r="E6" s="13" t="n">
+        <s:v>9338.54</s:v>
+      </s:c>
       <s:c r="F6" s="14" t="n">
         <s:v>2967.8</s:v>
       </s:c>
@@ -1506,8 +1526,12 @@
       <s:c r="C7" s="11" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="D7" s="12"/>
-      <s:c r="E7" s="13"/>
+      <s:c r="D7" s="12" t="n">
+        <s:v>36672.4</s:v>
+      </s:c>
+      <s:c r="E7" s="13" t="n">
+        <s:v>9335.7</s:v>
+      </s:c>
       <s:c r="F7" s="14" t="n">
         <s:v>2815.6</s:v>
       </s:c>
@@ -1530,8 +1554,12 @@
       <s:c r="C8" s="11" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="D8" s="12"/>
-      <s:c r="E8" s="13"/>
+      <s:c r="D8" s="12" t="n">
+        <s:v>36223.7</s:v>
+      </s:c>
+      <s:c r="E8" s="13" t="n">
+        <s:v>9362.13</s:v>
+      </s:c>
       <s:c r="F8" s="14" t="n">
         <s:v>2732.1</s:v>
       </s:c>
@@ -1554,8 +1582,12 @@
       <s:c r="C9" s="11" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="D9" s="12"/>
-      <s:c r="E9" s="13"/>
+      <s:c r="D9" s="12" t="n">
+        <s:v>35246</s:v>
+      </s:c>
+      <s:c r="E9" s="13" t="n">
+        <s:v>8988.3</s:v>
+      </s:c>
       <s:c r="F9" s="14" t="n">
         <s:v>2627.6</s:v>
       </s:c>
@@ -1578,8 +1610,12 @@
       <s:c r="C10" s="11" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="D10" s="12"/>
-      <s:c r="E10" s="13"/>
+      <s:c r="D10" s="12" t="n">
+        <s:v>34700.2</s:v>
+      </s:c>
+      <s:c r="E10" s="13" t="n">
+        <s:v>8865.03</s:v>
+      </s:c>
       <s:c r="F10" s="14" t="n">
         <s:v>2601.1</s:v>
       </s:c>
@@ -1602,8 +1638,12 @@
       <s:c r="C11" s="11" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="D11" s="12"/>
-      <s:c r="E11" s="13"/>
+      <s:c r="D11" s="12" t="n">
+        <s:v>34209.9</s:v>
+      </s:c>
+      <s:c r="E11" s="13" t="n">
+        <s:v>8710.62</s:v>
+      </s:c>
       <s:c r="F11" s="14" t="n">
         <s:v>2694</s:v>
       </s:c>
@@ -1626,8 +1666,12 @@
       <s:c r="C12" s="11" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="D12" s="12"/>
-      <s:c r="E12" s="13"/>
+      <s:c r="D12" s="12" t="n">
+        <s:v>33664.4</s:v>
+      </s:c>
+      <s:c r="E12" s="13" t="n">
+        <s:v>8555.61</s:v>
+      </s:c>
       <s:c r="F12" s="14" t="n">
         <s:v>2818.2</s:v>
       </s:c>
@@ -1650,8 +1694,12 @@
       <s:c r="C13" s="11" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="D13" s="12"/>
-      <s:c r="E13" s="13"/>
+      <s:c r="D13" s="12" t="n">
+        <s:v>33661.9</s:v>
+      </s:c>
+      <s:c r="E13" s="13" t="n">
+        <s:v>8250.53</s:v>
+      </s:c>
       <s:c r="F13" s="14" t="n">
         <s:v>3015.5</s:v>
       </s:c>
@@ -1674,8 +1722,12 @@
       <s:c r="C14" s="11" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D14" s="12"/>
-      <s:c r="E14" s="13"/>
+      <s:c r="D14" s="12" t="n">
+        <s:v>33196.1</s:v>
+      </s:c>
+      <s:c r="E14" s="13" t="n">
+        <s:v>8096.01</s:v>
+      </s:c>
       <s:c r="F14" s="14" t="n">
         <s:v>3161.4</s:v>
       </s:c>
@@ -1698,8 +1750,12 @@
       <s:c r="C15" s="11" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D15" s="12"/>
-      <s:c r="E15" s="13"/>
+      <s:c r="D15" s="12" t="n">
+        <s:v>32838.9</s:v>
+      </s:c>
+      <s:c r="E15" s="13" t="n">
+        <s:v>8090.55</s:v>
+      </s:c>
       <s:c r="F15" s="14" t="n">
         <s:v>3263.3</s:v>
       </s:c>
@@ -1722,8 +1778,12 @@
       <s:c r="C16" s="11" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D16" s="12"/>
-      <s:c r="E16" s="13"/>
+      <s:c r="D16" s="12" t="n">
+        <s:v>32568.3</s:v>
+      </s:c>
+      <s:c r="E16" s="13" t="n">
+        <s:v>8084.11</s:v>
+      </s:c>
       <s:c r="F16" s="14" t="n">
         <s:v>3368.6</s:v>
       </s:c>
@@ -1746,8 +1806,12 @@
       <s:c r="C17" s="11" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D17" s="12"/>
-      <s:c r="E17" s="13"/>
+      <s:c r="D17" s="12" t="n">
+        <s:v>32136.7</s:v>
+      </s:c>
+      <s:c r="E17" s="13" t="n">
+        <s:v>8077.25</s:v>
+      </s:c>
       <s:c r="F17" s="14" t="n">
         <s:v>3461.2</s:v>
       </s:c>
@@ -1770,8 +1834,12 @@
       <s:c r="C18" s="11" t="n">
         <s:v>5</s:v>
       </s:c>
-      <s:c r="D18" s="12"/>
-      <s:c r="E18" s="13"/>
+      <s:c r="D18" s="12" t="n">
+        <s:v>31941.1</s:v>
+      </s:c>
+      <s:c r="E18" s="13" t="n">
+        <s:v>8082.88</s:v>
+      </s:c>
       <s:c r="F18" s="14" t="n">
         <s:v>3495</s:v>
       </s:c>
@@ -1794,8 +1862,12 @@
       <s:c r="C19" s="11" t="n">
         <s:v>5</s:v>
       </s:c>
-      <s:c r="D19" s="12"/>
-      <s:c r="E19" s="13"/>
+      <s:c r="D19" s="12" t="n">
+        <s:v>31782.7</s:v>
+      </s:c>
+      <s:c r="E19" s="13" t="n">
+        <s:v>8075.39</s:v>
+      </s:c>
       <s:c r="F19" s="14" t="n">
         <s:v>3604.5</s:v>
       </s:c>
@@ -1818,8 +1890,12 @@
       <s:c r="C20" s="11" t="n">
         <s:v>5</s:v>
       </s:c>
-      <s:c r="D20" s="12"/>
-      <s:c r="E20" s="13"/>
+      <s:c r="D20" s="12" t="n">
+        <s:v>31951.4</s:v>
+      </s:c>
+      <s:c r="E20" s="13" t="n">
+        <s:v>7915.66</s:v>
+      </s:c>
       <s:c r="F20" s="14" t="n">
         <s:v>3668.5</s:v>
       </s:c>
@@ -1842,8 +1918,12 @@
       <s:c r="C21" s="11" t="n">
         <s:v>5</s:v>
       </s:c>
-      <s:c r="D21" s="12"/>
-      <s:c r="E21" s="13"/>
+      <s:c r="D21" s="12" t="n">
+        <s:v>31926.8</s:v>
+      </s:c>
+      <s:c r="E21" s="13" t="n">
+        <s:v>7755.86</s:v>
+      </s:c>
       <s:c r="F21" s="14" t="n">
         <s:v>3648.1</s:v>
       </s:c>
@@ -1866,8 +1946,12 @@
       <s:c r="C22" s="11" t="n">
         <s:v>6</s:v>
       </s:c>
-      <s:c r="D22" s="12"/>
-      <s:c r="E22" s="13"/>
+      <s:c r="D22" s="12" t="n">
+        <s:v>31853.9</s:v>
+      </s:c>
+      <s:c r="E22" s="13" t="n">
+        <s:v>7743.28</s:v>
+      </s:c>
       <s:c r="F22" s="14" t="n">
         <s:v>3558.4</s:v>
       </s:c>
@@ -1890,8 +1974,12 @@
       <s:c r="C23" s="11" t="n">
         <s:v>6</s:v>
       </s:c>
-      <s:c r="D23" s="12"/>
-      <s:c r="E23" s="13"/>
+      <s:c r="D23" s="12" t="n">
+        <s:v>32238.6</s:v>
+      </s:c>
+      <s:c r="E23" s="13" t="n">
+        <s:v>7738.16</s:v>
+      </s:c>
       <s:c r="F23" s="14" t="n">
         <s:v>3475.2</s:v>
       </s:c>
@@ -1914,8 +2002,12 @@
       <s:c r="C24" s="11" t="n">
         <s:v>6</s:v>
       </s:c>
-      <s:c r="D24" s="12"/>
-      <s:c r="E24" s="13"/>
+      <s:c r="D24" s="12" t="n">
+        <s:v>32472.1</s:v>
+      </s:c>
+      <s:c r="E24" s="13" t="n">
+        <s:v>7738.03</s:v>
+      </s:c>
       <s:c r="F24" s="14" t="n">
         <s:v>3503.4</s:v>
       </s:c>
@@ -1938,8 +2030,12 @@
       <s:c r="C25" s="11" t="n">
         <s:v>6</s:v>
       </s:c>
-      <s:c r="D25" s="12"/>
-      <s:c r="E25" s="13"/>
+      <s:c r="D25" s="12" t="n">
+        <s:v>32527.1</s:v>
+      </s:c>
+      <s:c r="E25" s="13" t="n">
+        <s:v>7737.66</s:v>
+      </s:c>
       <s:c r="F25" s="14" t="n">
         <s:v>3659.2</s:v>
       </s:c>
@@ -1962,8 +2058,12 @@
       <s:c r="C26" s="11" t="n">
         <s:v>7</s:v>
       </s:c>
-      <s:c r="D26" s="12"/>
-      <s:c r="E26" s="13"/>
+      <s:c r="D26" s="12" t="n">
+        <s:v>32809.7</s:v>
+      </s:c>
+      <s:c r="E26" s="13" t="n">
+        <s:v>7731.22</s:v>
+      </s:c>
       <s:c r="F26" s="14" t="n">
         <s:v>3827.4</s:v>
       </s:c>
@@ -1986,8 +2086,12 @@
       <s:c r="C27" s="11" t="n">
         <s:v>7</s:v>
       </s:c>
-      <s:c r="D27" s="12"/>
-      <s:c r="E27" s="13"/>
+      <s:c r="D27" s="12" t="n">
+        <s:v>32624.9</s:v>
+      </s:c>
+      <s:c r="E27" s="13" t="n">
+        <s:v>7741.99</s:v>
+      </s:c>
       <s:c r="F27" s="14" t="n">
         <s:v>4028.6</s:v>
       </s:c>
@@ -2010,8 +2114,12 @@
       <s:c r="C28" s="11" t="n">
         <s:v>7</s:v>
       </s:c>
-      <s:c r="D28" s="12"/>
-      <s:c r="E28" s="13"/>
+      <s:c r="D28" s="12" t="n">
+        <s:v>32363.8</s:v>
+      </s:c>
+      <s:c r="E28" s="13" t="n">
+        <s:v>7749.16</s:v>
+      </s:c>
       <s:c r="F28" s="14" t="n">
         <s:v>4337.2</s:v>
       </s:c>
@@ -2034,8 +2142,12 @@
       <s:c r="C29" s="11" t="n">
         <s:v>7</s:v>
       </s:c>
-      <s:c r="D29" s="12"/>
-      <s:c r="E29" s="13"/>
+      <s:c r="D29" s="12" t="n">
+        <s:v>31998.3</s:v>
+      </s:c>
+      <s:c r="E29" s="13" t="n">
+        <s:v>7520.17</s:v>
+      </s:c>
       <s:c r="F29" s="14" t="n">
         <s:v>4841.5</s:v>
       </s:c>
@@ -2058,8 +2170,12 @@
       <s:c r="C30" s="11" t="n">
         <s:v>8</s:v>
       </s:c>
-      <s:c r="D30" s="12"/>
-      <s:c r="E30" s="13"/>
+      <s:c r="D30" s="12" t="n">
+        <s:v>31548.9</s:v>
+      </s:c>
+      <s:c r="E30" s="13" t="n">
+        <s:v>7293.69</s:v>
+      </s:c>
       <s:c r="F30" s="14" t="n">
         <s:v>5231.5</s:v>
       </s:c>
@@ -2082,8 +2198,12 @@
       <s:c r="C31" s="11" t="n">
         <s:v>8</s:v>
       </s:c>
-      <s:c r="D31" s="12"/>
-      <s:c r="E31" s="13"/>
+      <s:c r="D31" s="12" t="n">
+        <s:v>31652.8</s:v>
+      </s:c>
+      <s:c r="E31" s="13" t="n">
+        <s:v>6521.36</s:v>
+      </s:c>
       <s:c r="F31" s="14" t="n">
         <s:v>5556.7</s:v>
       </s:c>
@@ -2106,8 +2226,12 @@
       <s:c r="C32" s="11" t="n">
         <s:v>8</s:v>
       </s:c>
-      <s:c r="D32" s="12"/>
-      <s:c r="E32" s="13"/>
+      <s:c r="D32" s="12" t="n">
+        <s:v>31742.5</s:v>
+      </s:c>
+      <s:c r="E32" s="13" t="n">
+        <s:v>5666.08</s:v>
+      </s:c>
       <s:c r="F32" s="14" t="n">
         <s:v>5794.1</s:v>
       </s:c>
@@ -2130,8 +2254,12 @@
       <s:c r="C33" s="11" t="n">
         <s:v>8</s:v>
       </s:c>
-      <s:c r="D33" s="12"/>
-      <s:c r="E33" s="13"/>
+      <s:c r="D33" s="12" t="n">
+        <s:v>31934.7</s:v>
+      </s:c>
+      <s:c r="E33" s="13" t="n">
+        <s:v>4955.21</s:v>
+      </s:c>
       <s:c r="F33" s="14" t="n">
         <s:v>6239.4</s:v>
       </s:c>
@@ -2154,8 +2282,12 @@
       <s:c r="C34" s="11" t="n">
         <s:v>9</s:v>
       </s:c>
-      <s:c r="D34" s="12"/>
-      <s:c r="E34" s="13"/>
+      <s:c r="D34" s="12" t="n">
+        <s:v>32523.8</s:v>
+      </s:c>
+      <s:c r="E34" s="13" t="n">
+        <s:v>4972.27</s:v>
+      </s:c>
       <s:c r="F34" s="14" t="n">
         <s:v>6939.1</s:v>
       </s:c>
@@ -2178,8 +2310,12 @@
       <s:c r="C35" s="11" t="n">
         <s:v>9</s:v>
       </s:c>
-      <s:c r="D35" s="12"/>
-      <s:c r="E35" s="13"/>
+      <s:c r="D35" s="12" t="n">
+        <s:v>32907</s:v>
+      </s:c>
+      <s:c r="E35" s="13" t="n">
+        <s:v>4971</s:v>
+      </s:c>
       <s:c r="F35" s="14" t="n">
         <s:v>7452.5</s:v>
       </s:c>
@@ -2202,8 +2338,12 @@
       <s:c r="C36" s="11" t="n">
         <s:v>9</s:v>
       </s:c>
-      <s:c r="D36" s="12"/>
-      <s:c r="E36" s="13"/>
+      <s:c r="D36" s="12" t="n">
+        <s:v>33145.3</s:v>
+      </s:c>
+      <s:c r="E36" s="13" t="n">
+        <s:v>4688.02</s:v>
+      </s:c>
       <s:c r="F36" s="14" t="n">
         <s:v>8145</s:v>
       </s:c>
@@ -2226,8 +2366,12 @@
       <s:c r="C37" s="11" t="n">
         <s:v>9</s:v>
       </s:c>
-      <s:c r="D37" s="12"/>
-      <s:c r="E37" s="13"/>
+      <s:c r="D37" s="12" t="n">
+        <s:v>33693</s:v>
+      </s:c>
+      <s:c r="E37" s="13" t="n">
+        <s:v>4402.06</s:v>
+      </s:c>
       <s:c r="F37" s="14" t="n">
         <s:v>8424.3</s:v>
       </s:c>
@@ -2250,8 +2394,12 @@
       <s:c r="C38" s="11" t="n">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="D38" s="12"/>
-      <s:c r="E38" s="13"/>
+      <s:c r="D38" s="12" t="n">
+        <s:v>34217</s:v>
+      </s:c>
+      <s:c r="E38" s="13" t="n">
+        <s:v>4417.33</s:v>
+      </s:c>
       <s:c r="F38" s="14" t="n">
         <s:v>8707.4</s:v>
       </s:c>
@@ -2274,8 +2422,12 @@
       <s:c r="C39" s="11" t="n">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="D39" s="12"/>
-      <s:c r="E39" s="13"/>
+      <s:c r="D39" s="12" t="n">
+        <s:v>34462.7</s:v>
+      </s:c>
+      <s:c r="E39" s="13" t="n">
+        <s:v>4449.42</s:v>
+      </s:c>
       <s:c r="F39" s="14" t="n">
         <s:v>8993.7</s:v>
       </s:c>
@@ -2298,8 +2450,12 @@
       <s:c r="C40" s="11" t="n">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="D40" s="12"/>
-      <s:c r="E40" s="13"/>
+      <s:c r="D40" s="12" t="n">
+        <s:v>34741.6</s:v>
+      </s:c>
+      <s:c r="E40" s="13" t="n">
+        <s:v>4471.09</s:v>
+      </s:c>
       <s:c r="F40" s="14" t="n">
         <s:v>9314.1</s:v>
       </s:c>
@@ -2322,8 +2478,12 @@
       <s:c r="C41" s="11" t="n">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="D41" s="12"/>
-      <s:c r="E41" s="13"/>
+      <s:c r="D41" s="12" t="n">
+        <s:v>34906.1</s:v>
+      </s:c>
+      <s:c r="E41" s="13" t="n">
+        <s:v>4482.54</s:v>
+      </s:c>
       <s:c r="F41" s="14" t="n">
         <s:v>9745.8</s:v>
       </s:c>
@@ -2346,8 +2506,12 @@
       <s:c r="C42" s="11" t="n">
         <s:v>11</s:v>
       </s:c>
-      <s:c r="D42" s="12"/>
-      <s:c r="E42" s="13"/>
+      <s:c r="D42" s="12" t="n">
+        <s:v>35381</s:v>
+      </s:c>
+      <s:c r="E42" s="13" t="n">
+        <s:v>4502.51</s:v>
+      </s:c>
       <s:c r="F42" s="14" t="n">
         <s:v>10302.8</s:v>
       </s:c>
@@ -2370,8 +2534,12 @@
       <s:c r="C43" s="11" t="n">
         <s:v>11</s:v>
       </s:c>
-      <s:c r="D43" s="12"/>
-      <s:c r="E43" s="13"/>
+      <s:c r="D43" s="12" t="n">
+        <s:v>35778.4</s:v>
+      </s:c>
+      <s:c r="E43" s="13" t="n">
+        <s:v>4514.64</s:v>
+      </s:c>
       <s:c r="F43" s="14" t="n">
         <s:v>10691.6</s:v>
       </s:c>
@@ -2394,8 +2562,12 @@
       <s:c r="C44" s="11" t="n">
         <s:v>11</s:v>
       </s:c>
-      <s:c r="D44" s="12"/>
-      <s:c r="E44" s="13"/>
+      <s:c r="D44" s="12" t="n">
+        <s:v>36115.8</s:v>
+      </s:c>
+      <s:c r="E44" s="13" t="n">
+        <s:v>4527.74</s:v>
+      </s:c>
       <s:c r="F44" s="14" t="n">
         <s:v>10676.6</s:v>
       </s:c>
@@ -2418,8 +2590,12 @@
       <s:c r="C45" s="11" t="n">
         <s:v>11</s:v>
       </s:c>
-      <s:c r="D45" s="12"/>
-      <s:c r="E45" s="13"/>
+      <s:c r="D45" s="12" t="n">
+        <s:v>36755.1</s:v>
+      </s:c>
+      <s:c r="E45" s="13" t="n">
+        <s:v>4537.07</s:v>
+      </s:c>
       <s:c r="F45" s="14" t="n">
         <s:v>10629.3</s:v>
       </s:c>
@@ -2442,8 +2618,12 @@
       <s:c r="C46" s="11" t="n">
         <s:v>12</s:v>
       </s:c>
-      <s:c r="D46" s="12"/>
-      <s:c r="E46" s="13"/>
+      <s:c r="D46" s="12" t="n">
+        <s:v>37788.8</s:v>
+      </s:c>
+      <s:c r="E46" s="13" t="n">
+        <s:v>4535.7</s:v>
+      </s:c>
       <s:c r="F46" s="14" t="n">
         <s:v>10844.3</s:v>
       </s:c>
@@ -2466,8 +2646,12 @@
       <s:c r="C47" s="11" t="n">
         <s:v>12</s:v>
       </s:c>
-      <s:c r="D47" s="12"/>
-      <s:c r="E47" s="13"/>
+      <s:c r="D47" s="12" t="n">
+        <s:v>37914.2</s:v>
+      </s:c>
+      <s:c r="E47" s="13" t="n">
+        <s:v>4551.61</s:v>
+      </s:c>
       <s:c r="F47" s="14" t="n">
         <s:v>10732.2</s:v>
       </s:c>
@@ -2490,8 +2674,12 @@
       <s:c r="C48" s="11" t="n">
         <s:v>12</s:v>
       </s:c>
-      <s:c r="D48" s="12"/>
-      <s:c r="E48" s="13"/>
+      <s:c r="D48" s="12" t="n">
+        <s:v>37902.5</s:v>
+      </s:c>
+      <s:c r="E48" s="13" t="n">
+        <s:v>4546.14</s:v>
+      </s:c>
       <s:c r="F48" s="14" t="n">
         <s:v>11005</s:v>
       </s:c>
@@ -2514,8 +2702,12 @@
       <s:c r="C49" s="11" t="n">
         <s:v>12</s:v>
       </s:c>
-      <s:c r="D49" s="12"/>
-      <s:c r="E49" s="13"/>
+      <s:c r="D49" s="12" t="n">
+        <s:v>37398.4</s:v>
+      </s:c>
+      <s:c r="E49" s="13" t="n">
+        <s:v>4543.85</s:v>
+      </s:c>
       <s:c r="F49" s="14" t="n">
         <s:v>10826.4</s:v>
       </s:c>
@@ -2538,8 +2730,12 @@
       <s:c r="C50" s="11" t="n">
         <s:v>13</s:v>
       </s:c>
-      <s:c r="D50" s="12"/>
-      <s:c r="E50" s="13"/>
+      <s:c r="D50" s="12" t="n">
+        <s:v>39733.7</s:v>
+      </s:c>
+      <s:c r="E50" s="13" t="n">
+        <s:v>5155.06</s:v>
+      </s:c>
       <s:c r="F50" s="14" t="n">
         <s:v>10950.5</s:v>
       </s:c>
@@ -2562,8 +2758,12 @@
       <s:c r="C51" s="11" t="n">
         <s:v>13</s:v>
       </s:c>
-      <s:c r="D51" s="12"/>
-      <s:c r="E51" s="13"/>
+      <s:c r="D51" s="12" t="n">
+        <s:v>39682.5</s:v>
+      </s:c>
+      <s:c r="E51" s="13" t="n">
+        <s:v>5746.47</s:v>
+      </s:c>
       <s:c r="F51" s="14" t="n">
         <s:v>10826.8</s:v>
       </s:c>
@@ -2586,8 +2786,12 @@
       <s:c r="C52" s="11" t="n">
         <s:v>13</s:v>
       </s:c>
-      <s:c r="D52" s="12"/>
-      <s:c r="E52" s="13"/>
+      <s:c r="D52" s="12" t="n">
+        <s:v>39799.4</s:v>
+      </s:c>
+      <s:c r="E52" s="13" t="n">
+        <s:v>6361.24</s:v>
+      </s:c>
       <s:c r="F52" s="14" t="n">
         <s:v>10814.9</s:v>
       </s:c>
@@ -2610,8 +2814,12 @@
       <s:c r="C53" s="11" t="n">
         <s:v>13</s:v>
       </s:c>
-      <s:c r="D53" s="12"/>
-      <s:c r="E53" s="13"/>
+      <s:c r="D53" s="12" t="n">
+        <s:v>39357.1</s:v>
+      </s:c>
+      <s:c r="E53" s="13" t="n">
+        <s:v>6958.55</s:v>
+      </s:c>
       <s:c r="F53" s="14" t="n">
         <s:v>11214</s:v>
       </s:c>
@@ -2634,8 +2842,12 @@
       <s:c r="C54" s="11" t="n">
         <s:v>14</s:v>
       </s:c>
-      <s:c r="D54" s="12"/>
-      <s:c r="E54" s="13"/>
+      <s:c r="D54" s="12" t="n">
+        <s:v>39344.2</s:v>
+      </s:c>
+      <s:c r="E54" s="13" t="n">
+        <s:v>7550.1</s:v>
+      </s:c>
       <s:c r="F54" s="14" t="n">
         <s:v>11076.9</s:v>
       </s:c>
@@ -2658,8 +2870,12 @@
       <s:c r="C55" s="11" t="n">
         <s:v>14</s:v>
       </s:c>
-      <s:c r="D55" s="12"/>
-      <s:c r="E55" s="13"/>
+      <s:c r="D55" s="12" t="n">
+        <s:v>38945.9</s:v>
+      </s:c>
+      <s:c r="E55" s="13" t="n">
+        <s:v>8148.18</s:v>
+      </s:c>
       <s:c r="F55" s="14" t="n">
         <s:v>11128.1</s:v>
       </s:c>
@@ -2682,8 +2898,12 @@
       <s:c r="C56" s="11" t="n">
         <s:v>14</s:v>
       </s:c>
-      <s:c r="D56" s="12"/>
-      <s:c r="E56" s="13"/>
+      <s:c r="D56" s="12" t="n">
+        <s:v>39013.1</s:v>
+      </s:c>
+      <s:c r="E56" s="13" t="n">
+        <s:v>8816.37</s:v>
+      </s:c>
       <s:c r="F56" s="14" t="n">
         <s:v>11118</s:v>
       </s:c>
@@ -2706,8 +2926,12 @@
       <s:c r="C57" s="11" t="n">
         <s:v>14</s:v>
       </s:c>
-      <s:c r="D57" s="12"/>
-      <s:c r="E57" s="13"/>
+      <s:c r="D57" s="12" t="n">
+        <s:v>38185.9</s:v>
+      </s:c>
+      <s:c r="E57" s="13" t="n">
+        <s:v>9066.77</s:v>
+      </s:c>
       <s:c r="F57" s="14" t="n">
         <s:v>11399.7</s:v>
       </s:c>
@@ -2730,8 +2954,12 @@
       <s:c r="C58" s="11" t="n">
         <s:v>15</s:v>
       </s:c>
-      <s:c r="D58" s="12"/>
-      <s:c r="E58" s="13"/>
+      <s:c r="D58" s="12" t="n">
+        <s:v>37890.1</s:v>
+      </s:c>
+      <s:c r="E58" s="13" t="n">
+        <s:v>9309.52</s:v>
+      </s:c>
       <s:c r="F58" s="14" t="n">
         <s:v>10966.3</s:v>
       </s:c>
@@ -2754,8 +2982,12 @@
       <s:c r="C59" s="11" t="n">
         <s:v>15</s:v>
       </s:c>
-      <s:c r="D59" s="12"/>
-      <s:c r="E59" s="13"/>
+      <s:c r="D59" s="12" t="n">
+        <s:v>38179.1</s:v>
+      </s:c>
+      <s:c r="E59" s="13" t="n">
+        <s:v>9555.81</s:v>
+      </s:c>
       <s:c r="F59" s="14" t="n">
         <s:v>10699.5</s:v>
       </s:c>
@@ -2778,8 +3010,12 @@
       <s:c r="C60" s="11" t="n">
         <s:v>15</s:v>
       </s:c>
-      <s:c r="D60" s="12"/>
-      <s:c r="E60" s="13"/>
+      <s:c r="D60" s="12" t="n">
+        <s:v>38447.8</s:v>
+      </s:c>
+      <s:c r="E60" s="13" t="n">
+        <s:v>9554.05</s:v>
+      </s:c>
       <s:c r="F60" s="14" t="n">
         <s:v>10535.6</s:v>
       </s:c>
@@ -2802,8 +3038,12 @@
       <s:c r="C61" s="11" t="n">
         <s:v>15</s:v>
       </s:c>
-      <s:c r="D61" s="12"/>
-      <s:c r="E61" s="13"/>
+      <s:c r="D61" s="12" t="n">
+        <s:v>38913.4</s:v>
+      </s:c>
+      <s:c r="E61" s="13" t="n">
+        <s:v>9737.35</s:v>
+      </s:c>
       <s:c r="F61" s="14" t="n">
         <s:v>10212.3</s:v>
       </s:c>
@@ -2826,8 +3066,12 @@
       <s:c r="C62" s="11" t="n">
         <s:v>16</s:v>
       </s:c>
-      <s:c r="D62" s="12"/>
-      <s:c r="E62" s="13"/>
+      <s:c r="D62" s="12" t="n">
+        <s:v>38902.3</s:v>
+      </s:c>
+      <s:c r="E62" s="13" t="n">
+        <s:v>10221.02</s:v>
+      </s:c>
       <s:c r="F62" s="14" t="n">
         <s:v>10114.5</s:v>
       </s:c>
@@ -2850,8 +3094,12 @@
       <s:c r="C63" s="11" t="n">
         <s:v>16</s:v>
       </s:c>
-      <s:c r="D63" s="12"/>
-      <s:c r="E63" s="13"/>
+      <s:c r="D63" s="12" t="n">
+        <s:v>39340.4</s:v>
+      </s:c>
+      <s:c r="E63" s="13" t="n">
+        <s:v>10708.03</s:v>
+      </s:c>
       <s:c r="F63" s="14" t="n">
         <s:v>9719.8</s:v>
       </s:c>
@@ -2874,8 +3122,12 @@
       <s:c r="C64" s="11" t="n">
         <s:v>16</s:v>
       </s:c>
-      <s:c r="D64" s="12"/>
-      <s:c r="E64" s="13"/>
+      <s:c r="D64" s="12" t="n">
+        <s:v>39943.8</s:v>
+      </s:c>
+      <s:c r="E64" s="13" t="n">
+        <s:v>10889.93</s:v>
+      </s:c>
       <s:c r="F64" s="14" t="n">
         <s:v>9341.6</s:v>
       </s:c>
@@ -2898,8 +3150,12 @@
       <s:c r="C65" s="11" t="n">
         <s:v>16</s:v>
       </s:c>
-      <s:c r="D65" s="12"/>
-      <s:c r="E65" s="13"/>
+      <s:c r="D65" s="12" t="n">
+        <s:v>40166.6</s:v>
+      </s:c>
+      <s:c r="E65" s="13" t="n">
+        <s:v>10868.84</s:v>
+      </s:c>
       <s:c r="F65" s="14" t="n">
         <s:v>8484</s:v>
       </s:c>
@@ -2922,8 +3178,12 @@
       <s:c r="C66" s="11" t="n">
         <s:v>17</s:v>
       </s:c>
-      <s:c r="D66" s="12"/>
-      <s:c r="E66" s="13"/>
+      <s:c r="D66" s="12" t="n">
+        <s:v>40591.8</s:v>
+      </s:c>
+      <s:c r="E66" s="13" t="n">
+        <s:v>10844.6</s:v>
+      </s:c>
       <s:c r="F66" s="14" t="n">
         <s:v>8018.9</s:v>
       </s:c>
@@ -2946,8 +3206,12 @@
       <s:c r="C67" s="11" t="n">
         <s:v>17</s:v>
       </s:c>
-      <s:c r="D67" s="12"/>
-      <s:c r="E67" s="13"/>
+      <s:c r="D67" s="12" t="n">
+        <s:v>41268.5</s:v>
+      </s:c>
+      <s:c r="E67" s="13" t="n">
+        <s:v>10965.26</s:v>
+      </s:c>
       <s:c r="F67" s="14" t="n">
         <s:v>7460</s:v>
       </s:c>
@@ -2970,8 +3234,12 @@
       <s:c r="C68" s="11" t="n">
         <s:v>17</s:v>
       </s:c>
-      <s:c r="D68" s="12"/>
-      <s:c r="E68" s="13"/>
+      <s:c r="D68" s="12" t="n">
+        <s:v>42185</s:v>
+      </s:c>
+      <s:c r="E68" s="13" t="n">
+        <s:v>11089.83</s:v>
+      </s:c>
       <s:c r="F68" s="14" t="n">
         <s:v>6972.7</s:v>
       </s:c>
@@ -2994,8 +3262,12 @@
       <s:c r="C69" s="11" t="n">
         <s:v>17</s:v>
       </s:c>
-      <s:c r="D69" s="12"/>
-      <s:c r="E69" s="13"/>
+      <s:c r="D69" s="12" t="n">
+        <s:v>43313.4</s:v>
+      </s:c>
+      <s:c r="E69" s="13" t="n">
+        <s:v>11058.23</s:v>
+      </s:c>
       <s:c r="F69" s="14" t="n">
         <s:v>6362.6</s:v>
       </s:c>
@@ -3018,8 +3290,12 @@
       <s:c r="C70" s="11" t="n">
         <s:v>18</s:v>
       </s:c>
-      <s:c r="D70" s="12"/>
-      <s:c r="E70" s="13"/>
+      <s:c r="D70" s="12" t="n">
+        <s:v>44187.8</s:v>
+      </s:c>
+      <s:c r="E70" s="13" t="n">
+        <s:v>11026.45</s:v>
+      </s:c>
       <s:c r="F70" s="14" t="n">
         <s:v>5761.1</s:v>
       </s:c>
@@ -3042,8 +3318,12 @@
       <s:c r="C71" s="11" t="n">
         <s:v>18</s:v>
       </s:c>
-      <s:c r="D71" s="12"/>
-      <s:c r="E71" s="13"/>
+      <s:c r="D71" s="12" t="n">
+        <s:v>44974.7</s:v>
+      </s:c>
+      <s:c r="E71" s="13" t="n">
+        <s:v>10999.3</s:v>
+      </s:c>
       <s:c r="F71" s="14" t="n">
         <s:v>5126.7</s:v>
       </s:c>
@@ -3066,8 +3346,12 @@
       <s:c r="C72" s="11" t="n">
         <s:v>18</s:v>
       </s:c>
-      <s:c r="D72" s="12"/>
-      <s:c r="E72" s="13"/>
+      <s:c r="D72" s="12" t="n">
+        <s:v>45789.8</s:v>
+      </s:c>
+      <s:c r="E72" s="13" t="n">
+        <s:v>11118.33</s:v>
+      </s:c>
       <s:c r="F72" s="14" t="n">
         <s:v>4642</s:v>
       </s:c>
@@ -3090,8 +3374,12 @@
       <s:c r="C73" s="11" t="n">
         <s:v>18</s:v>
       </s:c>
-      <s:c r="D73" s="12"/>
-      <s:c r="E73" s="13"/>
+      <s:c r="D73" s="12" t="n">
+        <s:v>46345.1</s:v>
+      </s:c>
+      <s:c r="E73" s="13" t="n">
+        <s:v>11343.74</s:v>
+      </s:c>
       <s:c r="F73" s="14" t="n">
         <s:v>4304.6</s:v>
       </s:c>
@@ -3114,8 +3402,12 @@
       <s:c r="C74" s="11" t="n">
         <s:v>19</s:v>
       </s:c>
-      <s:c r="D74" s="12"/>
-      <s:c r="E74" s="13"/>
+      <s:c r="D74" s="12" t="n">
+        <s:v>46803.8</s:v>
+      </s:c>
+      <s:c r="E74" s="13" t="n">
+        <s:v>11579.45</s:v>
+      </s:c>
       <s:c r="F74" s="14" t="n">
         <s:v>4081</s:v>
       </s:c>
@@ -3138,8 +3430,12 @@
       <s:c r="C75" s="11" t="n">
         <s:v>19</s:v>
       </s:c>
-      <s:c r="D75" s="12"/>
-      <s:c r="E75" s="13"/>
+      <s:c r="D75" s="12" t="n">
+        <s:v>46926.5</s:v>
+      </s:c>
+      <s:c r="E75" s="13" t="n">
+        <s:v>11818.18</s:v>
+      </s:c>
       <s:c r="F75" s="14" t="n">
         <s:v>3847.7</s:v>
       </s:c>
@@ -3162,8 +3458,12 @@
       <s:c r="C76" s="11" t="n">
         <s:v>19</s:v>
       </s:c>
-      <s:c r="D76" s="12"/>
-      <s:c r="E76" s="13"/>
+      <s:c r="D76" s="12" t="n">
+        <s:v>47183.9</s:v>
+      </s:c>
+      <s:c r="E76" s="13" t="n">
+        <s:v>11913.27</s:v>
+      </s:c>
       <s:c r="F76" s="14" t="n">
         <s:v>3759.9</s:v>
       </s:c>
@@ -3186,8 +3486,12 @@
       <s:c r="C77" s="11" t="n">
         <s:v>19</s:v>
       </s:c>
-      <s:c r="D77" s="12"/>
-      <s:c r="E77" s="13"/>
+      <s:c r="D77" s="12" t="n">
+        <s:v>47159</s:v>
+      </s:c>
+      <s:c r="E77" s="13" t="n">
+        <s:v>11910.67</s:v>
+      </s:c>
       <s:c r="F77" s="14" t="n">
         <s:v>3721.8</s:v>
       </s:c>
@@ -3210,8 +3514,12 @@
       <s:c r="C78" s="11" t="n">
         <s:v>20</s:v>
       </s:c>
-      <s:c r="D78" s="12"/>
-      <s:c r="E78" s="13"/>
+      <s:c r="D78" s="12" t="n">
+        <s:v>46978.3</s:v>
+      </s:c>
+      <s:c r="E78" s="13" t="n">
+        <s:v>11915.53</s:v>
+      </s:c>
       <s:c r="F78" s="14" t="n">
         <s:v>3801.3</s:v>
       </s:c>
@@ -3234,8 +3542,12 @@
       <s:c r="C79" s="11" t="n">
         <s:v>20</s:v>
       </s:c>
-      <s:c r="D79" s="12"/>
-      <s:c r="E79" s="13"/>
+      <s:c r="D79" s="12" t="n">
+        <s:v>47230</s:v>
+      </s:c>
+      <s:c r="E79" s="13" t="n">
+        <s:v>11920.99</s:v>
+      </s:c>
       <s:c r="F79" s="14" t="n">
         <s:v>3899.6</s:v>
       </s:c>
@@ -3258,8 +3570,12 @@
       <s:c r="C80" s="11" t="n">
         <s:v>20</s:v>
       </s:c>
-      <s:c r="D80" s="12"/>
-      <s:c r="E80" s="13"/>
+      <s:c r="D80" s="12" t="n">
+        <s:v>46930</s:v>
+      </s:c>
+      <s:c r="E80" s="13" t="n">
+        <s:v>11929.41</s:v>
+      </s:c>
       <s:c r="F80" s="14" t="n">
         <s:v>4026.8</s:v>
       </s:c>
@@ -3282,8 +3598,12 @@
       <s:c r="C81" s="11" t="n">
         <s:v>20</s:v>
       </s:c>
-      <s:c r="D81" s="12"/>
-      <s:c r="E81" s="13"/>
+      <s:c r="D81" s="12" t="n">
+        <s:v>46950.2</s:v>
+      </s:c>
+      <s:c r="E81" s="13" t="n">
+        <s:v>11939.23</s:v>
+      </s:c>
       <s:c r="F81" s="14" t="n">
         <s:v>4026.3</s:v>
       </s:c>
@@ -3306,8 +3626,12 @@
       <s:c r="C82" s="11" t="n">
         <s:v>21</s:v>
       </s:c>
-      <s:c r="D82" s="12"/>
-      <s:c r="E82" s="13"/>
+      <s:c r="D82" s="12" t="n">
+        <s:v>47015.3</s:v>
+      </s:c>
+      <s:c r="E82" s="13" t="n">
+        <s:v>11940</s:v>
+      </s:c>
       <s:c r="F82" s="14" t="n">
         <s:v>3874.1</s:v>
       </s:c>
@@ -3330,8 +3654,12 @@
       <s:c r="C83" s="11" t="n">
         <s:v>21</s:v>
       </s:c>
-      <s:c r="D83" s="12"/>
-      <s:c r="E83" s="13"/>
+      <s:c r="D83" s="12" t="n">
+        <s:v>46493.3</s:v>
+      </s:c>
+      <s:c r="E83" s="13" t="n">
+        <s:v>11890.63</s:v>
+      </s:c>
       <s:c r="F83" s="14" t="n">
         <s:v>3911.6</s:v>
       </s:c>
@@ -3354,8 +3682,12 @@
       <s:c r="C84" s="11" t="n">
         <s:v>21</s:v>
       </s:c>
-      <s:c r="D84" s="12"/>
-      <s:c r="E84" s="13"/>
+      <s:c r="D84" s="12" t="n">
+        <s:v>46649.8</s:v>
+      </s:c>
+      <s:c r="E84" s="13" t="n">
+        <s:v>11840.42</s:v>
+      </s:c>
       <s:c r="F84" s="14" t="n">
         <s:v>3928.6</s:v>
       </s:c>
@@ -3378,8 +3710,12 @@
       <s:c r="C85" s="11" t="n">
         <s:v>21</s:v>
       </s:c>
-      <s:c r="D85" s="12"/>
-      <s:c r="E85" s="13"/>
+      <s:c r="D85" s="12" t="n">
+        <s:v>46152.5</s:v>
+      </s:c>
+      <s:c r="E85" s="13" t="n">
+        <s:v>11789.18</s:v>
+      </s:c>
       <s:c r="F85" s="14" t="n">
         <s:v>3919.1</s:v>
       </s:c>
@@ -3402,8 +3738,12 @@
       <s:c r="C86" s="11" t="n">
         <s:v>22</s:v>
       </s:c>
-      <s:c r="D86" s="12"/>
-      <s:c r="E86" s="13"/>
+      <s:c r="D86" s="12" t="n">
+        <s:v>45903.2</s:v>
+      </s:c>
+      <s:c r="E86" s="13" t="n">
+        <s:v>11751.52</s:v>
+      </s:c>
       <s:c r="F86" s="14" t="n">
         <s:v>3873.5</s:v>
       </s:c>
@@ -3426,8 +3766,12 @@
       <s:c r="C87" s="11" t="n">
         <s:v>22</s:v>
       </s:c>
-      <s:c r="D87" s="12"/>
-      <s:c r="E87" s="13"/>
+      <s:c r="D87" s="12" t="n">
+        <s:v>45432.1</s:v>
+      </s:c>
+      <s:c r="E87" s="13" t="n">
+        <s:v>11750.02</s:v>
+      </s:c>
       <s:c r="F87" s="14" t="n">
         <s:v>3716.6</s:v>
       </s:c>
@@ -3450,8 +3794,12 @@
       <s:c r="C88" s="11" t="n">
         <s:v>22</s:v>
       </s:c>
-      <s:c r="D88" s="12"/>
-      <s:c r="E88" s="13"/>
+      <s:c r="D88" s="12" t="n">
+        <s:v>44977.2</s:v>
+      </s:c>
+      <s:c r="E88" s="13" t="n">
+        <s:v>11646.84</s:v>
+      </s:c>
       <s:c r="F88" s="14" t="n">
         <s:v>3640</s:v>
       </s:c>
@@ -3474,8 +3822,12 @@
       <s:c r="C89" s="11" t="n">
         <s:v>22</s:v>
       </s:c>
-      <s:c r="D89" s="12"/>
-      <s:c r="E89" s="13"/>
+      <s:c r="D89" s="12" t="n">
+        <s:v>44438.8</s:v>
+      </s:c>
+      <s:c r="E89" s="13" t="n">
+        <s:v>11392.75</s:v>
+      </s:c>
       <s:c r="F89" s="14" t="n">
         <s:v>3690.9</s:v>
       </s:c>
@@ -3498,8 +3850,12 @@
       <s:c r="C90" s="11" t="n">
         <s:v>23</s:v>
       </s:c>
-      <s:c r="D90" s="12"/>
-      <s:c r="E90" s="13"/>
+      <s:c r="D90" s="12" t="n">
+        <s:v>43699.3</s:v>
+      </s:c>
+      <s:c r="E90" s="13" t="n">
+        <s:v>11137.08</s:v>
+      </s:c>
       <s:c r="F90" s="14" t="n">
         <s:v>3771.2</s:v>
       </s:c>
@@ -3522,8 +3878,12 @@
       <s:c r="C91" s="11" t="n">
         <s:v>23</s:v>
       </s:c>
-      <s:c r="D91" s="12"/>
-      <s:c r="E91" s="13"/>
+      <s:c r="D91" s="12" t="n">
+        <s:v>43080.2</s:v>
+      </s:c>
+      <s:c r="E91" s="13" t="n">
+        <s:v>10731.75</s:v>
+      </s:c>
       <s:c r="F91" s="14" t="n">
         <s:v>3815.3</s:v>
       </s:c>
@@ -3546,8 +3906,12 @@
       <s:c r="C92" s="11" t="n">
         <s:v>23</s:v>
       </s:c>
-      <s:c r="D92" s="12"/>
-      <s:c r="E92" s="13"/>
+      <s:c r="D92" s="12" t="n">
+        <s:v>42205.6</s:v>
+      </s:c>
+      <s:c r="E92" s="13" t="n">
+        <s:v>10426.8</s:v>
+      </s:c>
       <s:c r="F92" s="14" t="n">
         <s:v>3966.7</s:v>
       </s:c>
@@ -3570,8 +3934,12 @@
       <s:c r="C93" s="11" t="n">
         <s:v>23</s:v>
       </s:c>
-      <s:c r="D93" s="12"/>
-      <s:c r="E93" s="13"/>
+      <s:c r="D93" s="12" t="n">
+        <s:v>41356.4</s:v>
+      </s:c>
+      <s:c r="E93" s="13" t="n">
+        <s:v>10222.33</s:v>
+      </s:c>
       <s:c r="F93" s="14" t="n">
         <s:v>4068.4</s:v>
       </s:c>
@@ -3594,8 +3962,12 @@
       <s:c r="C94" s="11" t="n">
         <s:v>24</s:v>
       </s:c>
-      <s:c r="D94" s="12"/>
-      <s:c r="E94" s="13"/>
+      <s:c r="D94" s="12" t="n">
+        <s:v>40520.3</s:v>
+      </s:c>
+      <s:c r="E94" s="13" t="n">
+        <s:v>10018.11</s:v>
+      </s:c>
       <s:c r="F94" s="14" t="n">
         <s:v>4220.4</s:v>
       </s:c>
@@ -3618,8 +3990,12 @@
       <s:c r="C95" s="11" t="n">
         <s:v>24</s:v>
       </s:c>
-      <s:c r="D95" s="12"/>
-      <s:c r="E95" s="13"/>
+      <s:c r="D95" s="12" t="n">
+        <s:v>39664.3</s:v>
+      </s:c>
+      <s:c r="E95" s="13" t="n">
+        <s:v>9816.39</s:v>
+      </s:c>
       <s:c r="F95" s="14" t="n">
         <s:v>4265.8</s:v>
       </s:c>
@@ -3642,8 +4018,12 @@
       <s:c r="C96" s="11" t="n">
         <s:v>24</s:v>
       </s:c>
-      <s:c r="D96" s="12"/>
-      <s:c r="E96" s="13"/>
+      <s:c r="D96" s="12" t="n">
+        <s:v>38768.3</s:v>
+      </s:c>
+      <s:c r="E96" s="13" t="n">
+        <s:v>9615.46</s:v>
+      </s:c>
       <s:c r="F96" s="14" t="n">
         <s:v>4363.9</s:v>
       </s:c>
@@ -3668,8 +4048,12 @@
       <s:c r="C97" s="11" t="n">
         <s:v>24</s:v>
       </s:c>
-      <s:c r="D97" s="12"/>
-      <s:c r="E97" s="13"/>
+      <s:c r="D97" s="12" t="n">
+        <s:v>38425.1</s:v>
+      </s:c>
+      <s:c r="E97" s="13" t="n">
+        <s:v>9533.48</s:v>
+      </s:c>
       <s:c r="F97" s="14" t="n">
         <s:v>4475.8</s:v>
       </s:c>
@@ -3854,8 +4238,12 @@
       <s:c r="C2" s="1" t="n">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="D2" s="1"/>
-      <s:c r="E2" s="1"/>
+      <s:c r="D2" s="1" t="n">
+        <s:v>438.2</s:v>
+      </s:c>
+      <s:c r="E2" s="1" t="n">
+        <s:v>395.07</s:v>
+      </s:c>
       <s:c r="F2" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -3900,8 +4288,12 @@
       <s:c r="C3" s="1" t="n">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="D3" s="1"/>
-      <s:c r="E3" s="1"/>
+      <s:c r="D3" s="1" t="n">
+        <s:v>438.2</s:v>
+      </s:c>
+      <s:c r="E3" s="1" t="n">
+        <s:v>395.07</s:v>
+      </s:c>
       <s:c r="F3" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -3946,8 +4338,12 @@
       <s:c r="C4" s="1" t="n">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="D4" s="1"/>
-      <s:c r="E4" s="1"/>
+      <s:c r="D4" s="1" t="n">
+        <s:v>438.2</s:v>
+      </s:c>
+      <s:c r="E4" s="1" t="n">
+        <s:v>392.39</s:v>
+      </s:c>
       <s:c r="F4" s="1" t="n">
         <s:v>30</s:v>
       </s:c>
@@ -3992,8 +4388,12 @@
       <s:c r="C5" s="1" t="n">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="D5" s="1"/>
-      <s:c r="E5" s="1"/>
+      <s:c r="D5" s="1" t="n">
+        <s:v>442.76</s:v>
+      </s:c>
+      <s:c r="E5" s="1" t="n">
+        <s:v>409</s:v>
+      </s:c>
       <s:c r="F5" s="1" t="n">
         <s:v>30</s:v>
       </s:c>
@@ -4038,8 +4438,12 @@
       <s:c r="C6" s="1" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="D6" s="1"/>
-      <s:c r="E6" s="1"/>
+      <s:c r="D6" s="1" t="n">
+        <s:v>510.79</s:v>
+      </s:c>
+      <s:c r="E6" s="1" t="n">
+        <s:v>425.23</s:v>
+      </s:c>
       <s:c r="F6" s="1" t="n">
         <s:v>30</s:v>
       </s:c>
@@ -4084,8 +4488,12 @@
       <s:c r="C7" s="1" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="D7" s="1"/>
-      <s:c r="E7" s="1"/>
+      <s:c r="D7" s="1" t="n">
+        <s:v>510.23</s:v>
+      </s:c>
+      <s:c r="E7" s="1" t="n">
+        <s:v>423.72</s:v>
+      </s:c>
       <s:c r="F7" s="1" t="n">
         <s:v>30</s:v>
       </s:c>
@@ -4130,8 +4538,12 @@
       <s:c r="C8" s="1" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="D8" s="1"/>
-      <s:c r="E8" s="1"/>
+      <s:c r="D8" s="1" t="n">
+        <s:v>510.23</s:v>
+      </s:c>
+      <s:c r="E8" s="1" t="n">
+        <s:v>424.44</s:v>
+      </s:c>
       <s:c r="F8" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -4176,8 +4588,12 @@
       <s:c r="C9" s="1" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="D9" s="1"/>
-      <s:c r="E9" s="1"/>
+      <s:c r="D9" s="1" t="n">
+        <s:v>510.79</s:v>
+      </s:c>
+      <s:c r="E9" s="1" t="n">
+        <s:v>426.98</s:v>
+      </s:c>
       <s:c r="F9" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -4222,8 +4638,12 @@
       <s:c r="C10" s="1" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="D10" s="1"/>
-      <s:c r="E10" s="1"/>
+      <s:c r="D10" s="1" t="n">
+        <s:v>425.38</s:v>
+      </s:c>
+      <s:c r="E10" s="1" t="n">
+        <s:v>421.98</s:v>
+      </s:c>
       <s:c r="F10" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -4268,8 +4688,12 @@
       <s:c r="C11" s="1" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="D11" s="1"/>
-      <s:c r="E11" s="1"/>
+      <s:c r="D11" s="1" t="n">
+        <s:v>425.38</s:v>
+      </s:c>
+      <s:c r="E11" s="1" t="n">
+        <s:v>423.72</s:v>
+      </s:c>
       <s:c r="F11" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -4314,8 +4738,12 @@
       <s:c r="C12" s="1" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="D12" s="1"/>
-      <s:c r="E12" s="1"/>
+      <s:c r="D12" s="1" t="n">
+        <s:v>425.38</s:v>
+      </s:c>
+      <s:c r="E12" s="1" t="n">
+        <s:v>413.47</s:v>
+      </s:c>
       <s:c r="F12" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -4360,8 +4788,12 @@
       <s:c r="C13" s="1" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="D13" s="1"/>
-      <s:c r="E13" s="1"/>
+      <s:c r="D13" s="1" t="n">
+        <s:v>425.38</s:v>
+      </s:c>
+      <s:c r="E13" s="1" t="n">
+        <s:v>393.76</s:v>
+      </s:c>
       <s:c r="F13" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -4406,8 +4838,12 @@
       <s:c r="C14" s="1" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D14" s="1"/>
-      <s:c r="E14" s="1"/>
+      <s:c r="D14" s="1" t="n">
+        <s:v>425.38</s:v>
+      </s:c>
+      <s:c r="E14" s="1" t="n">
+        <s:v>392.51</s:v>
+      </s:c>
       <s:c r="F14" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -4452,8 +4888,12 @@
       <s:c r="C15" s="1" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D15" s="1"/>
-      <s:c r="E15" s="1"/>
+      <s:c r="D15" s="1" t="n">
+        <s:v>425.38</s:v>
+      </s:c>
+      <s:c r="E15" s="1" t="n">
+        <s:v>391.07</s:v>
+      </s:c>
       <s:c r="F15" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -4498,8 +4938,12 @@
       <s:c r="C16" s="1" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D16" s="1"/>
-      <s:c r="E16" s="1"/>
+      <s:c r="D16" s="1" t="n">
+        <s:v>425.38</s:v>
+      </s:c>
+      <s:c r="E16" s="1" t="n">
+        <s:v>373.13</s:v>
+      </s:c>
       <s:c r="F16" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -4544,8 +4988,12 @@
       <s:c r="C17" s="1" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D17" s="1"/>
-      <s:c r="E17" s="1"/>
+      <s:c r="D17" s="1" t="n">
+        <s:v>425.38</s:v>
+      </s:c>
+      <s:c r="E17" s="1" t="n">
+        <s:v>370.29</s:v>
+      </s:c>
       <s:c r="F17" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -4590,8 +5038,12 @@
       <s:c r="C18" s="1" t="n">
         <s:v>5</s:v>
       </s:c>
-      <s:c r="D18" s="1"/>
-      <s:c r="E18" s="1"/>
+      <s:c r="D18" s="1" t="n">
+        <s:v>421.97</s:v>
+      </s:c>
+      <s:c r="E18" s="1" t="n">
+        <s:v>373.54</s:v>
+      </s:c>
       <s:c r="F18" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -4636,8 +5088,12 @@
       <s:c r="C19" s="1" t="n">
         <s:v>5</s:v>
       </s:c>
-      <s:c r="D19" s="1"/>
-      <s:c r="E19" s="1"/>
+      <s:c r="D19" s="1" t="n">
+        <s:v>421.97</s:v>
+      </s:c>
+      <s:c r="E19" s="1" t="n">
+        <s:v>365.17</s:v>
+      </s:c>
       <s:c r="F19" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -4682,8 +5138,12 @@
       <s:c r="C20" s="1" t="n">
         <s:v>5</s:v>
       </s:c>
-      <s:c r="D20" s="1"/>
-      <s:c r="E20" s="1"/>
+      <s:c r="D20" s="1" t="n">
+        <s:v>421.97</s:v>
+      </s:c>
+      <s:c r="E20" s="1" t="n">
+        <s:v>364.98</s:v>
+      </s:c>
       <s:c r="F20" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -4728,8 +5188,12 @@
       <s:c r="C21" s="1" t="n">
         <s:v>5</s:v>
       </s:c>
-      <s:c r="D21" s="1"/>
-      <s:c r="E21" s="1"/>
+      <s:c r="D21" s="1" t="n">
+        <s:v>421.97</s:v>
+      </s:c>
+      <s:c r="E21" s="1" t="n">
+        <s:v>365.69</s:v>
+      </s:c>
       <s:c r="F21" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -4774,8 +5238,12 @@
       <s:c r="C22" s="1" t="n">
         <s:v>6</s:v>
       </s:c>
-      <s:c r="D22" s="1"/>
-      <s:c r="E22" s="1"/>
+      <s:c r="D22" s="1" t="n">
+        <s:v>438.2</s:v>
+      </s:c>
+      <s:c r="E22" s="1" t="n">
+        <s:v>366.79</s:v>
+      </s:c>
       <s:c r="F22" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -4820,8 +5288,12 @@
       <s:c r="C23" s="1" t="n">
         <s:v>6</s:v>
       </s:c>
-      <s:c r="D23" s="1"/>
-      <s:c r="E23" s="1"/>
+      <s:c r="D23" s="1" t="n">
+        <s:v>442.76</s:v>
+      </s:c>
+      <s:c r="E23" s="1" t="n">
+        <s:v>367.04</s:v>
+      </s:c>
       <s:c r="F23" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -4866,8 +5338,12 @@
       <s:c r="C24" s="1" t="n">
         <s:v>6</s:v>
       </s:c>
-      <s:c r="D24" s="1"/>
-      <s:c r="E24" s="1"/>
+      <s:c r="D24" s="1" t="n">
+        <s:v>442.76</s:v>
+      </s:c>
+      <s:c r="E24" s="1" t="n">
+        <s:v>371.22</s:v>
+      </s:c>
       <s:c r="F24" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -4912,8 +5388,12 @@
       <s:c r="C25" s="1" t="n">
         <s:v>6</s:v>
       </s:c>
-      <s:c r="D25" s="1"/>
-      <s:c r="E25" s="1"/>
+      <s:c r="D25" s="1" t="n">
+        <s:v>442.76</s:v>
+      </s:c>
+      <s:c r="E25" s="1" t="n">
+        <s:v>376.95</s:v>
+      </s:c>
       <s:c r="F25" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -4958,8 +5438,12 @@
       <s:c r="C26" s="1" t="n">
         <s:v>7</s:v>
       </s:c>
-      <s:c r="D26" s="1"/>
-      <s:c r="E26" s="1"/>
+      <s:c r="D26" s="1" t="n">
+        <s:v>425.57</s:v>
+      </s:c>
+      <s:c r="E26" s="1" t="n">
+        <s:v>375.72</s:v>
+      </s:c>
       <s:c r="F26" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -5004,8 +5488,12 @@
       <s:c r="C27" s="1" t="n">
         <s:v>7</s:v>
       </s:c>
-      <s:c r="D27" s="1"/>
-      <s:c r="E27" s="1"/>
+      <s:c r="D27" s="1" t="n">
+        <s:v>421.97</s:v>
+      </s:c>
+      <s:c r="E27" s="1" t="n">
+        <s:v>382.48</s:v>
+      </s:c>
       <s:c r="F27" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -5050,8 +5538,12 @@
       <s:c r="C28" s="1" t="n">
         <s:v>7</s:v>
       </s:c>
-      <s:c r="D28" s="1"/>
-      <s:c r="E28" s="1"/>
+      <s:c r="D28" s="1" t="n">
+        <s:v>421.97</s:v>
+      </s:c>
+      <s:c r="E28" s="1" t="n">
+        <s:v>376.95</s:v>
+      </s:c>
       <s:c r="F28" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -5096,8 +5588,12 @@
       <s:c r="C29" s="1" t="n">
         <s:v>7</s:v>
       </s:c>
-      <s:c r="D29" s="1"/>
-      <s:c r="E29" s="1"/>
+      <s:c r="D29" s="1" t="n">
+        <s:v>421.97</s:v>
+      </s:c>
+      <s:c r="E29" s="1" t="n">
+        <s:v>363.57</s:v>
+      </s:c>
       <s:c r="F29" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -5142,8 +5638,12 @@
       <s:c r="C30" s="1" t="n">
         <s:v>8</s:v>
       </s:c>
-      <s:c r="D30" s="1"/>
-      <s:c r="E30" s="1"/>
+      <s:c r="D30" s="1" t="n">
+        <s:v>438.2</s:v>
+      </s:c>
+      <s:c r="E30" s="1" t="n">
+        <s:v>393.8</s:v>
+      </s:c>
       <s:c r="F30" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -5188,8 +5688,12 @@
       <s:c r="C31" s="1" t="n">
         <s:v>8</s:v>
       </s:c>
-      <s:c r="D31" s="1"/>
-      <s:c r="E31" s="1"/>
+      <s:c r="D31" s="1" t="n">
+        <s:v>425.38</s:v>
+      </s:c>
+      <s:c r="E31" s="1" t="n">
+        <s:v>360.29</s:v>
+      </s:c>
       <s:c r="F31" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -5234,8 +5738,12 @@
       <s:c r="C32" s="1" t="n">
         <s:v>8</s:v>
       </s:c>
-      <s:c r="D32" s="1"/>
-      <s:c r="E32" s="1"/>
+      <s:c r="D32" s="1" t="n">
+        <s:v>425.38</s:v>
+      </s:c>
+      <s:c r="E32" s="1" t="n">
+        <s:v>342.3</s:v>
+      </s:c>
       <s:c r="F32" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -5280,8 +5788,12 @@
       <s:c r="C33" s="1" t="n">
         <s:v>8</s:v>
       </s:c>
-      <s:c r="D33" s="1"/>
-      <s:c r="E33" s="1"/>
+      <s:c r="D33" s="1" t="n">
+        <s:v>425.38</s:v>
+      </s:c>
+      <s:c r="E33" s="1" t="n">
+        <s:v>339.04</s:v>
+      </s:c>
       <s:c r="F33" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -5326,8 +5838,12 @@
       <s:c r="C34" s="1" t="n">
         <s:v>9</s:v>
       </s:c>
-      <s:c r="D34" s="1"/>
-      <s:c r="E34" s="1"/>
+      <s:c r="D34" s="1" t="n">
+        <s:v>382.07</s:v>
+      </s:c>
+      <s:c r="E34" s="1" t="n">
+        <s:v>337.14</s:v>
+      </s:c>
       <s:c r="F34" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -5372,8 +5888,12 @@
       <s:c r="C35" s="1" t="n">
         <s:v>9</s:v>
       </s:c>
-      <s:c r="D35" s="1"/>
-      <s:c r="E35" s="1"/>
+      <s:c r="D35" s="1" t="n">
+        <s:v>393.35</s:v>
+      </s:c>
+      <s:c r="E35" s="1" t="n">
+        <s:v>339.04</s:v>
+      </s:c>
       <s:c r="F35" s="1" t="n">
         <s:v>-60</s:v>
       </s:c>
@@ -5418,8 +5938,12 @@
       <s:c r="C36" s="1" t="n">
         <s:v>9</s:v>
       </s:c>
-      <s:c r="D36" s="1"/>
-      <s:c r="E36" s="1"/>
+      <s:c r="D36" s="1" t="n">
+        <s:v>393.35</s:v>
+      </s:c>
+      <s:c r="E36" s="1" t="n">
+        <s:v>339.48</s:v>
+      </s:c>
       <s:c r="F36" s="1" t="n">
         <s:v>-120</s:v>
       </s:c>
@@ -5464,8 +5988,12 @@
       <s:c r="C37" s="1" t="n">
         <s:v>9</s:v>
       </s:c>
-      <s:c r="D37" s="1"/>
-      <s:c r="E37" s="1"/>
+      <s:c r="D37" s="1" t="n">
+        <s:v>382.07</s:v>
+      </s:c>
+      <s:c r="E37" s="1" t="n">
+        <s:v>337.01</s:v>
+      </s:c>
       <s:c r="F37" s="1" t="n">
         <s:v>-150</s:v>
       </s:c>
@@ -5510,8 +6038,12 @@
       <s:c r="C38" s="1" t="n">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="D38" s="1"/>
-      <s:c r="E38" s="1"/>
+      <s:c r="D38" s="1" t="n">
+        <s:v>365.27</s:v>
+      </s:c>
+      <s:c r="E38" s="1" t="n">
+        <s:v>339.86</s:v>
+      </s:c>
       <s:c r="F38" s="1" t="n">
         <s:v>-310</s:v>
       </s:c>
@@ -5556,8 +6088,12 @@
       <s:c r="C39" s="1" t="n">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="D39" s="1"/>
-      <s:c r="E39" s="1"/>
+      <s:c r="D39" s="1" t="n">
+        <s:v>365.27</s:v>
+      </s:c>
+      <s:c r="E39" s="1" t="n">
+        <s:v>341.23</s:v>
+      </s:c>
       <s:c r="F39" s="1" t="n">
         <s:v>-480</s:v>
       </s:c>
@@ -5602,8 +6138,12 @@
       <s:c r="C40" s="1" t="n">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="D40" s="1"/>
-      <s:c r="E40" s="1"/>
+      <s:c r="D40" s="1" t="n">
+        <s:v>365.27</s:v>
+      </s:c>
+      <s:c r="E40" s="1" t="n">
+        <s:v>339.14</s:v>
+      </s:c>
       <s:c r="F40" s="1" t="n">
         <s:v>-510</s:v>
       </s:c>
@@ -5648,8 +6188,12 @@
       <s:c r="C41" s="1" t="n">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="D41" s="1"/>
-      <s:c r="E41" s="1"/>
+      <s:c r="D41" s="1" t="n">
+        <s:v>340.47</s:v>
+      </s:c>
+      <s:c r="E41" s="1" t="n">
+        <s:v>337.01</s:v>
+      </s:c>
       <s:c r="F41" s="1" t="n">
         <s:v>-410</s:v>
       </s:c>
@@ -5694,8 +6238,12 @@
       <s:c r="C42" s="1" t="n">
         <s:v>11</s:v>
       </s:c>
-      <s:c r="D42" s="1"/>
-      <s:c r="E42" s="1"/>
+      <s:c r="D42" s="1" t="n">
+        <s:v>340.47</s:v>
+      </s:c>
+      <s:c r="E42" s="1" t="n">
+        <s:v>339.04</s:v>
+      </s:c>
       <s:c r="F42" s="1" t="n">
         <s:v>-280</s:v>
       </s:c>
@@ -5740,8 +6288,12 @@
       <s:c r="C43" s="1" t="n">
         <s:v>11</s:v>
       </s:c>
-      <s:c r="D43" s="1"/>
-      <s:c r="E43" s="1"/>
+      <s:c r="D43" s="1" t="n">
+        <s:v>365.27</s:v>
+      </s:c>
+      <s:c r="E43" s="1" t="n">
+        <s:v>339.3</s:v>
+      </s:c>
       <s:c r="F43" s="1" t="n">
         <s:v>-290</s:v>
       </s:c>
@@ -5786,8 +6338,12 @@
       <s:c r="C44" s="1" t="n">
         <s:v>11</s:v>
       </s:c>
-      <s:c r="D44" s="1"/>
-      <s:c r="E44" s="1"/>
+      <s:c r="D44" s="1" t="n">
+        <s:v>365.27</s:v>
+      </s:c>
+      <s:c r="E44" s="1" t="n">
+        <s:v>343.25</s:v>
+      </s:c>
       <s:c r="F44" s="1" t="n">
         <s:v>-290</s:v>
       </s:c>
@@ -5832,8 +6388,12 @@
       <s:c r="C45" s="1" t="n">
         <s:v>11</s:v>
       </s:c>
-      <s:c r="D45" s="1"/>
-      <s:c r="E45" s="1"/>
+      <s:c r="D45" s="1" t="n">
+        <s:v>365.27</s:v>
+      </s:c>
+      <s:c r="E45" s="1" t="n">
+        <s:v>339.3</s:v>
+      </s:c>
       <s:c r="F45" s="1" t="n">
         <s:v>-230</s:v>
       </s:c>
@@ -5878,8 +6438,12 @@
       <s:c r="C46" s="1" t="n">
         <s:v>12</s:v>
       </s:c>
-      <s:c r="D46" s="1"/>
-      <s:c r="E46" s="1"/>
+      <s:c r="D46" s="1" t="n">
+        <s:v>365.27</s:v>
+      </s:c>
+      <s:c r="E46" s="1" t="n">
+        <s:v>336.79</s:v>
+      </s:c>
       <s:c r="F46" s="1" t="n">
         <s:v>-100</s:v>
       </s:c>
@@ -5924,8 +6488,12 @@
       <s:c r="C47" s="1" t="n">
         <s:v>12</s:v>
       </s:c>
-      <s:c r="D47" s="1"/>
-      <s:c r="E47" s="1"/>
+      <s:c r="D47" s="1" t="n">
+        <s:v>365.27</s:v>
+      </s:c>
+      <s:c r="E47" s="1" t="n">
+        <s:v>343.25</s:v>
+      </s:c>
       <s:c r="F47" s="1" t="n">
         <s:v>-70</s:v>
       </s:c>
@@ -5970,8 +6538,12 @@
       <s:c r="C48" s="1" t="n">
         <s:v>12</s:v>
       </s:c>
-      <s:c r="D48" s="1"/>
-      <s:c r="E48" s="1"/>
+      <s:c r="D48" s="1" t="n">
+        <s:v>391.79</s:v>
+      </s:c>
+      <s:c r="E48" s="1" t="n">
+        <s:v>350.7</s:v>
+      </s:c>
       <s:c r="F48" s="1" t="n">
         <s:v>-40</s:v>
       </s:c>
@@ -6016,8 +6588,12 @@
       <s:c r="C49" s="1" t="n">
         <s:v>12</s:v>
       </s:c>
-      <s:c r="D49" s="1"/>
-      <s:c r="E49" s="1"/>
+      <s:c r="D49" s="1" t="n">
+        <s:v>365.27</s:v>
+      </s:c>
+      <s:c r="E49" s="1" t="n">
+        <s:v>365.39</s:v>
+      </s:c>
       <s:c r="F49" s="1" t="n">
         <s:v>-30</s:v>
       </s:c>
@@ -6062,8 +6638,12 @@
       <s:c r="C50" s="1" t="n">
         <s:v>13</s:v>
       </s:c>
-      <s:c r="D50" s="1"/>
-      <s:c r="E50" s="1"/>
+      <s:c r="D50" s="1" t="n">
+        <s:v>421.97</s:v>
+      </s:c>
+      <s:c r="E50" s="1" t="n">
+        <s:v>390.14</s:v>
+      </s:c>
       <s:c r="F50" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -6108,8 +6688,12 @@
       <s:c r="C51" s="1" t="n">
         <s:v>13</s:v>
       </s:c>
-      <s:c r="D51" s="1"/>
-      <s:c r="E51" s="1"/>
+      <s:c r="D51" s="1" t="n">
+        <s:v>421.97</s:v>
+      </s:c>
+      <s:c r="E51" s="1" t="n">
+        <s:v>390.14</s:v>
+      </s:c>
       <s:c r="F51" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -6154,8 +6738,12 @@
       <s:c r="C52" s="1" t="n">
         <s:v>13</s:v>
       </s:c>
-      <s:c r="D52" s="1"/>
-      <s:c r="E52" s="1"/>
+      <s:c r="D52" s="1" t="n">
+        <s:v>421.97</s:v>
+      </s:c>
+      <s:c r="E52" s="1" t="n">
+        <s:v>376.95</s:v>
+      </s:c>
       <s:c r="F52" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -6200,8 +6788,12 @@
       <s:c r="C53" s="1" t="n">
         <s:v>13</s:v>
       </s:c>
-      <s:c r="D53" s="1"/>
-      <s:c r="E53" s="1"/>
+      <s:c r="D53" s="1" t="n">
+        <s:v>425.38</s:v>
+      </s:c>
+      <s:c r="E53" s="1" t="n">
+        <s:v>367.01</s:v>
+      </s:c>
       <s:c r="F53" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -6246,8 +6838,12 @@
       <s:c r="C54" s="1" t="n">
         <s:v>14</s:v>
       </s:c>
-      <s:c r="D54" s="1"/>
-      <s:c r="E54" s="1"/>
+      <s:c r="D54" s="1" t="n">
+        <s:v>425.38</s:v>
+      </s:c>
+      <s:c r="E54" s="1" t="n">
+        <s:v>366.16</s:v>
+      </s:c>
       <s:c r="F54" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -6292,8 +6888,12 @@
       <s:c r="C55" s="1" t="n">
         <s:v>14</s:v>
       </s:c>
-      <s:c r="D55" s="1"/>
-      <s:c r="E55" s="1"/>
+      <s:c r="D55" s="1" t="n">
+        <s:v>403.27</s:v>
+      </s:c>
+      <s:c r="E55" s="1" t="n">
+        <s:v>391.42</s:v>
+      </s:c>
       <s:c r="F55" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -6338,8 +6938,12 @@
       <s:c r="C56" s="1" t="n">
         <s:v>14</s:v>
       </s:c>
-      <s:c r="D56" s="1"/>
-      <s:c r="E56" s="1"/>
+      <s:c r="D56" s="1" t="n">
+        <s:v>403.27</s:v>
+      </s:c>
+      <s:c r="E56" s="1" t="n">
+        <s:v>390.01</s:v>
+      </s:c>
       <s:c r="F56" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -6384,8 +6988,12 @@
       <s:c r="C57" s="1" t="n">
         <s:v>14</s:v>
       </s:c>
-      <s:c r="D57" s="1"/>
-      <s:c r="E57" s="1"/>
+      <s:c r="D57" s="1" t="n">
+        <s:v>403.27</s:v>
+      </s:c>
+      <s:c r="E57" s="1" t="n">
+        <s:v>391.42</s:v>
+      </s:c>
       <s:c r="F57" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -6430,8 +7038,12 @@
       <s:c r="C58" s="1" t="n">
         <s:v>15</s:v>
       </s:c>
-      <s:c r="D58" s="1"/>
-      <s:c r="E58" s="1"/>
+      <s:c r="D58" s="1" t="n">
+        <s:v>393.35</s:v>
+      </s:c>
+      <s:c r="E58" s="1" t="n">
+        <s:v>409</s:v>
+      </s:c>
       <s:c r="F58" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -6476,8 +7088,12 @@
       <s:c r="C59" s="1" t="n">
         <s:v>15</s:v>
       </s:c>
-      <s:c r="D59" s="1"/>
-      <s:c r="E59" s="1"/>
+      <s:c r="D59" s="1" t="n">
+        <s:v>421.97</s:v>
+      </s:c>
+      <s:c r="E59" s="1" t="n">
+        <s:v>390.01</s:v>
+      </s:c>
       <s:c r="F59" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -6522,8 +7138,12 @@
       <s:c r="C60" s="1" t="n">
         <s:v>15</s:v>
       </s:c>
-      <s:c r="D60" s="1"/>
-      <s:c r="E60" s="1"/>
+      <s:c r="D60" s="1" t="n">
+        <s:v>421.97</s:v>
+      </s:c>
+      <s:c r="E60" s="1" t="n">
+        <s:v>381.36</s:v>
+      </s:c>
       <s:c r="F60" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -6568,8 +7188,12 @@
       <s:c r="C61" s="1" t="n">
         <s:v>15</s:v>
       </s:c>
-      <s:c r="D61" s="1"/>
-      <s:c r="E61" s="1"/>
+      <s:c r="D61" s="1" t="n">
+        <s:v>421.97</s:v>
+      </s:c>
+      <s:c r="E61" s="1" t="n">
+        <s:v>417.76</s:v>
+      </s:c>
       <s:c r="F61" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -6614,8 +7238,12 @@
       <s:c r="C62" s="1" t="n">
         <s:v>16</s:v>
       </s:c>
-      <s:c r="D62" s="1"/>
-      <s:c r="E62" s="1"/>
+      <s:c r="D62" s="1" t="n">
+        <s:v>421.97</s:v>
+      </s:c>
+      <s:c r="E62" s="1" t="n">
+        <s:v>400.57</s:v>
+      </s:c>
       <s:c r="F62" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -6660,8 +7288,12 @@
       <s:c r="C63" s="1" t="n">
         <s:v>16</s:v>
       </s:c>
-      <s:c r="D63" s="1"/>
-      <s:c r="E63" s="1"/>
+      <s:c r="D63" s="1" t="n">
+        <s:v>421.97</s:v>
+      </s:c>
+      <s:c r="E63" s="1" t="n">
+        <s:v>445.3</s:v>
+      </s:c>
       <s:c r="F63" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -6706,8 +7338,12 @@
       <s:c r="C64" s="1" t="n">
         <s:v>16</s:v>
       </s:c>
-      <s:c r="D64" s="1"/>
-      <s:c r="E64" s="1"/>
+      <s:c r="D64" s="1" t="n">
+        <s:v>421.97</s:v>
+      </s:c>
+      <s:c r="E64" s="1" t="n">
+        <s:v>422.1</s:v>
+      </s:c>
       <s:c r="F64" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -6752,8 +7388,12 @@
       <s:c r="C65" s="1" t="n">
         <s:v>16</s:v>
       </s:c>
-      <s:c r="D65" s="1"/>
-      <s:c r="E65" s="1"/>
+      <s:c r="D65" s="1" t="n">
+        <s:v>421.97</s:v>
+      </s:c>
+      <s:c r="E65" s="1" t="n">
+        <s:v>425.85</s:v>
+      </s:c>
       <s:c r="F65" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -6798,8 +7438,12 @@
       <s:c r="C66" s="1" t="n">
         <s:v>17</s:v>
       </s:c>
-      <s:c r="D66" s="1"/>
-      <s:c r="E66" s="1"/>
+      <s:c r="D66" s="1" t="n">
+        <s:v>425.57</s:v>
+      </s:c>
+      <s:c r="E66" s="1" t="n">
+        <s:v>441.32</s:v>
+      </s:c>
       <s:c r="F66" s="1" t="n">
         <s:v>30</s:v>
       </s:c>
@@ -6844,8 +7488,12 @@
       <s:c r="C67" s="1" t="n">
         <s:v>17</s:v>
       </s:c>
-      <s:c r="D67" s="1"/>
-      <s:c r="E67" s="1"/>
+      <s:c r="D67" s="1" t="n">
+        <s:v>438.2</s:v>
+      </s:c>
+      <s:c r="E67" s="1" t="n">
+        <s:v>445.3</s:v>
+      </s:c>
       <s:c r="F67" s="1" t="n">
         <s:v>60</s:v>
       </s:c>
@@ -6890,8 +7538,12 @@
       <s:c r="C68" s="1" t="n">
         <s:v>17</s:v>
       </s:c>
-      <s:c r="D68" s="1"/>
-      <s:c r="E68" s="1"/>
+      <s:c r="D68" s="1" t="n">
+        <s:v>438.2</s:v>
+      </s:c>
+      <s:c r="E68" s="1" t="n">
+        <s:v>459.5</s:v>
+      </s:c>
       <s:c r="F68" s="1" t="n">
         <s:v>100</s:v>
       </s:c>
@@ -6936,8 +7588,12 @@
       <s:c r="C69" s="1" t="n">
         <s:v>17</s:v>
       </s:c>
-      <s:c r="D69" s="1"/>
-      <s:c r="E69" s="1"/>
+      <s:c r="D69" s="1" t="n">
+        <s:v>438.2</s:v>
+      </s:c>
+      <s:c r="E69" s="1" t="n">
+        <s:v>467.95</s:v>
+      </s:c>
       <s:c r="F69" s="1" t="n">
         <s:v>160</s:v>
       </s:c>
@@ -6982,8 +7638,12 @@
       <s:c r="C70" s="1" t="n">
         <s:v>18</s:v>
       </s:c>
-      <s:c r="D70" s="1"/>
-      <s:c r="E70" s="1"/>
+      <s:c r="D70" s="1" t="n">
+        <s:v>483.58</s:v>
+      </s:c>
+      <s:c r="E70" s="1" t="n">
+        <s:v>473.29</s:v>
+      </s:c>
       <s:c r="F70" s="1" t="n">
         <s:v>160</s:v>
       </s:c>
@@ -7028,8 +7688,12 @@
       <s:c r="C71" s="1" t="n">
         <s:v>18</s:v>
       </s:c>
-      <s:c r="D71" s="1"/>
-      <s:c r="E71" s="1"/>
+      <s:c r="D71" s="1" t="n">
+        <s:v>483.58</s:v>
+      </s:c>
+      <s:c r="E71" s="1" t="n">
+        <s:v>473.29</s:v>
+      </s:c>
       <s:c r="F71" s="1" t="n">
         <s:v>160</s:v>
       </s:c>
@@ -7074,8 +7738,12 @@
       <s:c r="C72" s="1" t="n">
         <s:v>18</s:v>
       </s:c>
-      <s:c r="D72" s="1"/>
-      <s:c r="E72" s="1"/>
+      <s:c r="D72" s="1" t="n">
+        <s:v>483.58</s:v>
+      </s:c>
+      <s:c r="E72" s="1" t="n">
+        <s:v>480.39</s:v>
+      </s:c>
       <s:c r="F72" s="1" t="n">
         <s:v>100</s:v>
       </s:c>
@@ -7120,8 +7788,12 @@
       <s:c r="C73" s="1" t="n">
         <s:v>18</s:v>
       </s:c>
-      <s:c r="D73" s="1"/>
-      <s:c r="E73" s="1"/>
+      <s:c r="D73" s="1" t="n">
+        <s:v>483.58</s:v>
+      </s:c>
+      <s:c r="E73" s="1" t="n">
+        <s:v>472.39</s:v>
+      </s:c>
       <s:c r="F73" s="1" t="n">
         <s:v>100</s:v>
       </s:c>
@@ -7166,8 +7838,12 @@
       <s:c r="C74" s="1" t="n">
         <s:v>19</s:v>
       </s:c>
-      <s:c r="D74" s="1"/>
-      <s:c r="E74" s="1"/>
+      <s:c r="D74" s="1" t="n">
+        <s:v>410.89</s:v>
+      </s:c>
+      <s:c r="E74" s="1" t="n">
+        <s:v>473.17</s:v>
+      </s:c>
       <s:c r="F74" s="1" t="n">
         <s:v>100</s:v>
       </s:c>
@@ -7212,8 +7888,12 @@
       <s:c r="C75" s="1" t="n">
         <s:v>19</s:v>
       </s:c>
-      <s:c r="D75" s="1"/>
-      <s:c r="E75" s="1"/>
+      <s:c r="D75" s="1" t="n">
+        <s:v>410.89</s:v>
+      </s:c>
+      <s:c r="E75" s="1" t="n">
+        <s:v>473.77</s:v>
+      </s:c>
       <s:c r="F75" s="1" t="n">
         <s:v>90</s:v>
       </s:c>
@@ -7258,8 +7938,12 @@
       <s:c r="C76" s="1" t="n">
         <s:v>19</s:v>
       </s:c>
-      <s:c r="D76" s="1"/>
-      <s:c r="E76" s="1"/>
+      <s:c r="D76" s="1" t="n">
+        <s:v>410.89</s:v>
+      </s:c>
+      <s:c r="E76" s="1" t="n">
+        <s:v>483.1</s:v>
+      </s:c>
       <s:c r="F76" s="1" t="n">
         <s:v>30</s:v>
       </s:c>
@@ -7304,8 +7988,12 @@
       <s:c r="C77" s="1" t="n">
         <s:v>19</s:v>
       </s:c>
-      <s:c r="D77" s="1"/>
-      <s:c r="E77" s="1"/>
+      <s:c r="D77" s="1" t="n">
+        <s:v>410.89</s:v>
+      </s:c>
+      <s:c r="E77" s="1" t="n">
+        <s:v>484.19</s:v>
+      </s:c>
       <s:c r="F77" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -7350,8 +8038,12 @@
       <s:c r="C78" s="1" t="n">
         <s:v>20</s:v>
       </s:c>
-      <s:c r="D78" s="1"/>
-      <s:c r="E78" s="1"/>
+      <s:c r="D78" s="1" t="n">
+        <s:v>425.57</s:v>
+      </s:c>
+      <s:c r="E78" s="1" t="n">
+        <s:v>481.48</s:v>
+      </s:c>
       <s:c r="F78" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -7396,8 +8088,12 @@
       <s:c r="C79" s="1" t="n">
         <s:v>20</s:v>
       </s:c>
-      <s:c r="D79" s="1"/>
-      <s:c r="E79" s="1"/>
+      <s:c r="D79" s="1" t="n">
+        <s:v>425.57</s:v>
+      </s:c>
+      <s:c r="E79" s="1" t="n">
+        <s:v>479.27</s:v>
+      </s:c>
       <s:c r="F79" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -7442,8 +8138,12 @@
       <s:c r="C80" s="1" t="n">
         <s:v>20</s:v>
       </s:c>
-      <s:c r="D80" s="1"/>
-      <s:c r="E80" s="1"/>
+      <s:c r="D80" s="1" t="n">
+        <s:v>425.57</s:v>
+      </s:c>
+      <s:c r="E80" s="1" t="n">
+        <s:v>478.67</s:v>
+      </s:c>
       <s:c r="F80" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -7488,8 +8188,12 @@
       <s:c r="C81" s="1" t="n">
         <s:v>20</s:v>
       </s:c>
-      <s:c r="D81" s="1"/>
-      <s:c r="E81" s="1"/>
+      <s:c r="D81" s="1" t="n">
+        <s:v>425.57</s:v>
+      </s:c>
+      <s:c r="E81" s="1" t="n">
+        <s:v>471.55</s:v>
+      </s:c>
       <s:c r="F81" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -7534,8 +8238,12 @@
       <s:c r="C82" s="1" t="n">
         <s:v>21</s:v>
       </s:c>
-      <s:c r="D82" s="1"/>
-      <s:c r="E82" s="1"/>
+      <s:c r="D82" s="1" t="n">
+        <s:v>425.38</s:v>
+      </s:c>
+      <s:c r="E82" s="1" t="n">
+        <s:v>469.44</s:v>
+      </s:c>
       <s:c r="F82" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -7580,8 +8288,12 @@
       <s:c r="C83" s="1" t="n">
         <s:v>21</s:v>
       </s:c>
-      <s:c r="D83" s="1"/>
-      <s:c r="E83" s="1"/>
+      <s:c r="D83" s="1" t="n">
+        <s:v>438.2</s:v>
+      </s:c>
+      <s:c r="E83" s="1" t="n">
+        <s:v>470.57</s:v>
+      </s:c>
       <s:c r="F83" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -7626,8 +8338,12 @@
       <s:c r="C84" s="1" t="n">
         <s:v>21</s:v>
       </s:c>
-      <s:c r="D84" s="1"/>
-      <s:c r="E84" s="1"/>
+      <s:c r="D84" s="1" t="n">
+        <s:v>438.2</s:v>
+      </s:c>
+      <s:c r="E84" s="1" t="n">
+        <s:v>466.54</s:v>
+      </s:c>
       <s:c r="F84" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -7672,8 +8388,12 @@
       <s:c r="C85" s="1" t="n">
         <s:v>21</s:v>
       </s:c>
-      <s:c r="D85" s="1"/>
-      <s:c r="E85" s="1"/>
+      <s:c r="D85" s="1" t="n">
+        <s:v>425.38</s:v>
+      </s:c>
+      <s:c r="E85" s="1" t="n">
+        <s:v>468.14</s:v>
+      </s:c>
       <s:c r="F85" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -7718,8 +8438,12 @@
       <s:c r="C86" s="1" t="n">
         <s:v>22</s:v>
       </s:c>
-      <s:c r="D86" s="1"/>
-      <s:c r="E86" s="1"/>
+      <s:c r="D86" s="1" t="n">
+        <s:v>425.57</s:v>
+      </s:c>
+      <s:c r="E86" s="1" t="n">
+        <s:v>461.54</s:v>
+      </s:c>
       <s:c r="F86" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -7764,8 +8488,12 @@
       <s:c r="C87" s="1" t="n">
         <s:v>22</s:v>
       </s:c>
-      <s:c r="D87" s="1"/>
-      <s:c r="E87" s="1"/>
+      <s:c r="D87" s="1" t="n">
+        <s:v>425.57</s:v>
+      </s:c>
+      <s:c r="E87" s="1" t="n">
+        <s:v>467.95</s:v>
+      </s:c>
       <s:c r="F87" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -7810,8 +8538,12 @@
       <s:c r="C88" s="1" t="n">
         <s:v>22</s:v>
       </s:c>
-      <s:c r="D88" s="1"/>
-      <s:c r="E88" s="1"/>
+      <s:c r="D88" s="1" t="n">
+        <s:v>421.97</s:v>
+      </s:c>
+      <s:c r="E88" s="1" t="n">
+        <s:v>469.29</s:v>
+      </s:c>
       <s:c r="F88" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -7856,8 +8588,12 @@
       <s:c r="C89" s="1" t="n">
         <s:v>22</s:v>
       </s:c>
-      <s:c r="D89" s="1"/>
-      <s:c r="E89" s="1"/>
+      <s:c r="D89" s="1" t="n">
+        <s:v>421.97</s:v>
+      </s:c>
+      <s:c r="E89" s="1" t="n">
+        <s:v>472.92</s:v>
+      </s:c>
       <s:c r="F89" s="1" t="n">
         <s:v>60</s:v>
       </s:c>
@@ -7902,8 +8638,12 @@
       <s:c r="C90" s="1" t="n">
         <s:v>23</s:v>
       </s:c>
-      <s:c r="D90" s="1"/>
-      <s:c r="E90" s="1"/>
+      <s:c r="D90" s="1" t="n">
+        <s:v>438.2</s:v>
+      </s:c>
+      <s:c r="E90" s="1" t="n">
+        <s:v>466.85</s:v>
+      </s:c>
       <s:c r="F90" s="1" t="n">
         <s:v>220</s:v>
       </s:c>
@@ -7948,8 +8688,12 @@
       <s:c r="C91" s="1" t="n">
         <s:v>23</s:v>
       </s:c>
-      <s:c r="D91" s="1"/>
-      <s:c r="E91" s="1"/>
+      <s:c r="D91" s="1" t="n">
+        <s:v>438.2</s:v>
+      </s:c>
+      <s:c r="E91" s="1" t="n">
+        <s:v>460.42</s:v>
+      </s:c>
       <s:c r="F91" s="1" t="n">
         <s:v>220</s:v>
       </s:c>
@@ -7994,8 +8738,12 @@
       <s:c r="C92" s="1" t="n">
         <s:v>23</s:v>
       </s:c>
-      <s:c r="D92" s="1"/>
-      <s:c r="E92" s="1"/>
+      <s:c r="D92" s="1" t="n">
+        <s:v>438.2</s:v>
+      </s:c>
+      <s:c r="E92" s="1" t="n">
+        <s:v>455.89</s:v>
+      </s:c>
       <s:c r="F92" s="1" t="n">
         <s:v>220</s:v>
       </s:c>
@@ -8040,8 +8788,12 @@
       <s:c r="C93" s="1" t="n">
         <s:v>23</s:v>
       </s:c>
-      <s:c r="D93" s="1"/>
-      <s:c r="E93" s="1"/>
+      <s:c r="D93" s="1" t="n">
+        <s:v>438.2</s:v>
+      </s:c>
+      <s:c r="E93" s="1" t="n">
+        <s:v>452.67</s:v>
+      </s:c>
       <s:c r="F93" s="1" t="n">
         <s:v>220</s:v>
       </s:c>
@@ -8086,8 +8838,12 @@
       <s:c r="C94" s="1" t="n">
         <s:v>24</s:v>
       </s:c>
-      <s:c r="D94" s="1"/>
-      <s:c r="E94" s="1"/>
+      <s:c r="D94" s="1" t="n">
+        <s:v>438.2</s:v>
+      </s:c>
+      <s:c r="E94" s="1" t="n">
+        <s:v>442.82</s:v>
+      </s:c>
       <s:c r="F94" s="1" t="n">
         <s:v>220</s:v>
       </s:c>
@@ -8132,8 +8888,12 @@
       <s:c r="C95" s="1" t="n">
         <s:v>24</s:v>
       </s:c>
-      <s:c r="D95" s="1"/>
-      <s:c r="E95" s="1"/>
+      <s:c r="D95" s="1" t="n">
+        <s:v>438.2</s:v>
+      </s:c>
+      <s:c r="E95" s="1" t="n">
+        <s:v>433.57</s:v>
+      </s:c>
       <s:c r="F95" s="1" t="n">
         <s:v>220</s:v>
       </s:c>
@@ -8178,8 +8938,12 @@
       <s:c r="C96" s="1" t="n">
         <s:v>24</s:v>
       </s:c>
-      <s:c r="D96" s="1"/>
-      <s:c r="E96" s="1"/>
+      <s:c r="D96" s="1" t="n">
+        <s:v>438.2</s:v>
+      </s:c>
+      <s:c r="E96" s="1" t="n">
+        <s:v>438.83</s:v>
+      </s:c>
       <s:c r="F96" s="1" t="n">
         <s:v>120</s:v>
       </s:c>
@@ -8226,8 +8990,12 @@
       <s:c r="C97" s="1" t="n">
         <s:v>24</s:v>
       </s:c>
-      <s:c r="D97" s="1"/>
-      <s:c r="E97" s="1"/>
+      <s:c r="D97" s="1" t="n">
+        <s:v>438.2</s:v>
+      </s:c>
+      <s:c r="E97" s="1" t="n">
+        <s:v>434.85</s:v>
+      </s:c>
       <s:c r="F97" s="1" t="n">
         <s:v>60</s:v>
       </s:c>
